--- a/LISTAS/mi/BISAGRAS FICHAS carpintero.xlsx
+++ b/LISTAS/mi/BISAGRAS FICHAS carpintero.xlsx
@@ -877,14 +877,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="35" t="n">
-        <v>45180.47733258679</v>
+        <v>45237</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="17">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -936,16 +932,6 @@
       <c r="C12" s="40" t="n"/>
       <c r="D12" s="40" t="n"/>
     </row>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
     <row r="23">
       <c r="C23" s="19" t="n"/>
     </row>
@@ -1001,7 +987,7 @@
       </c>
       <c r="C29" s="41" t="n"/>
       <c r="D29" s="43" t="n">
-        <v>174.985</v>
+        <v>201.233</v>
       </c>
     </row>
     <row r="30" ht="19.5" customHeight="1" s="17">
@@ -1017,7 +1003,7 @@
       </c>
       <c r="C30" s="41" t="n"/>
       <c r="D30" s="43" t="n">
-        <v>185.113</v>
+        <v>212.88</v>
       </c>
     </row>
     <row r="31" ht="19.5" customHeight="1" s="17">
@@ -1033,10 +1019,9 @@
       </c>
       <c r="C31" s="41" t="n"/>
       <c r="D31" s="43" t="n">
-        <v>199.332</v>
-      </c>
-    </row>
-    <row r="32"/>
+        <v>229.232</v>
+      </c>
+    </row>
     <row r="33">
       <c r="A33" s="26" t="inlineStr">
         <is>
@@ -1044,7 +1029,6 @@
         </is>
       </c>
     </row>
-    <row r="34"/>
     <row r="35" ht="18" customHeight="1" s="17">
       <c r="A35" s="37" t="n"/>
       <c r="B35" s="37" t="n"/>
@@ -1057,33 +1041,28 @@
     </row>
     <row r="37" ht="16.5" customHeight="1" s="17"/>
     <row r="38" ht="16.5" customHeight="1" s="17"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
     <row r="42" ht="19.5" customHeight="1" s="17">
       <c r="A42" s="7" t="n"/>
     </row>
-    <row r="43"/>
     <row r="44">
       <c r="A44" s="5" t="n"/>
     </row>
-    <row r="45"/>
     <row r="46">
       <c r="A46" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B30:C30"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A10:D10"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="B31:C31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/BISAGRAS FICHAS carpintero.xlsx
+++ b/LISTAS/mi/BISAGRAS FICHAS carpintero.xlsx
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C30" s="41" t="n"/>
       <c r="D30" s="43" t="n">
-        <v>212.88</v>
+        <v>250</v>
       </c>
     </row>
     <row r="31" ht="19.5" customHeight="1" s="17">
@@ -1052,17 +1052,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A12:D12"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B35:C35"/>
     <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B28:C28"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B36:C36"/>
     <mergeCell ref="B29:C29"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B35:C35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/BISAGRAS FICHAS carpintero.xlsx
+++ b/LISTAS/mi/BISAGRAS FICHAS carpintero.xlsx
@@ -877,7 +877,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="35" t="n">
-        <v>45237</v>
+        <v>45252</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
@@ -1052,17 +1052,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A1:D1"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B29:C29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/BISAGRAS FICHAS carpintero.xlsx
+++ b/LISTAS/mi/BISAGRAS FICHAS carpintero.xlsx
@@ -877,7 +877,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="35" t="n">
-        <v>45252</v>
+        <v>45253</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
@@ -1052,17 +1052,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A12:D12"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B35:C35"/>
     <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B28:C28"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B36:C36"/>
     <mergeCell ref="B29:C29"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B35:C35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/BISAGRAS FICHAS carpintero.xlsx
+++ b/LISTAS/mi/BISAGRAS FICHAS carpintero.xlsx
@@ -877,7 +877,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="35" t="n">
-        <v>45253</v>
+        <v>45256</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
@@ -1052,17 +1052,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A1:D1"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B29:C29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/BISAGRAS FICHAS carpintero.xlsx
+++ b/LISTAS/mi/BISAGRAS FICHAS carpintero.xlsx
@@ -877,7 +877,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="35" t="n">
-        <v>45256</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>

--- a/LISTAS/mi/BISAGRAS FICHAS carpintero.xlsx
+++ b/LISTAS/mi/BISAGRAS FICHAS carpintero.xlsx
@@ -877,10 +877,14 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="35" t="n">
-        <v>45266</v>
+        <v>45261.57769723675</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="17">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -932,6 +936,16 @@
       <c r="C12" s="40" t="n"/>
       <c r="D12" s="40" t="n"/>
     </row>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
     <row r="23">
       <c r="C23" s="19" t="n"/>
     </row>
@@ -987,7 +1001,7 @@
       </c>
       <c r="C29" s="41" t="n"/>
       <c r="D29" s="43" t="n">
-        <v>201.233</v>
+        <v>243.49</v>
       </c>
     </row>
     <row r="30" ht="19.5" customHeight="1" s="17">
@@ -1003,7 +1017,7 @@
       </c>
       <c r="C30" s="41" t="n"/>
       <c r="D30" s="43" t="n">
-        <v>250</v>
+        <v>257.58</v>
       </c>
     </row>
     <row r="31" ht="19.5" customHeight="1" s="17">
@@ -1019,9 +1033,10 @@
       </c>
       <c r="C31" s="41" t="n"/>
       <c r="D31" s="43" t="n">
-        <v>229.232</v>
-      </c>
-    </row>
+        <v>277.37</v>
+      </c>
+    </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" s="26" t="inlineStr">
         <is>
@@ -1029,6 +1044,7 @@
         </is>
       </c>
     </row>
+    <row r="34"/>
     <row r="35" ht="18" customHeight="1" s="17">
       <c r="A35" s="37" t="n"/>
       <c r="B35" s="37" t="n"/>
@@ -1041,28 +1057,33 @@
     </row>
     <row r="37" ht="16.5" customHeight="1" s="17"/>
     <row r="38" ht="16.5" customHeight="1" s="17"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
     <row r="42" ht="19.5" customHeight="1" s="17">
       <c r="A42" s="7" t="n"/>
     </row>
+    <row r="43"/>
     <row r="44">
       <c r="A44" s="5" t="n"/>
     </row>
+    <row r="45"/>
     <row r="46">
       <c r="A46" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
     <mergeCell ref="B30:C30"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B29:C29"/>
     <mergeCell ref="A12:D12"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B36:C36"/>
     <mergeCell ref="B31:C31"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B35:C35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/BISAGRAS FICHAS carpintero.xlsx
+++ b/LISTAS/mi/BISAGRAS FICHAS carpintero.xlsx
@@ -877,14 +877,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="35" t="n">
-        <v>45261.57769723675</v>
+        <v>45286</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="17">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -936,16 +932,6 @@
       <c r="C12" s="40" t="n"/>
       <c r="D12" s="40" t="n"/>
     </row>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
     <row r="23">
       <c r="C23" s="19" t="n"/>
     </row>
@@ -1001,7 +987,7 @@
       </c>
       <c r="C29" s="41" t="n"/>
       <c r="D29" s="43" t="n">
-        <v>243.49</v>
+        <v>201.233</v>
       </c>
     </row>
     <row r="30" ht="19.5" customHeight="1" s="17">
@@ -1017,7 +1003,7 @@
       </c>
       <c r="C30" s="41" t="n"/>
       <c r="D30" s="43" t="n">
-        <v>257.58</v>
+        <v>250</v>
       </c>
     </row>
     <row r="31" ht="19.5" customHeight="1" s="17">
@@ -1033,10 +1019,9 @@
       </c>
       <c r="C31" s="41" t="n"/>
       <c r="D31" s="43" t="n">
-        <v>277.37</v>
-      </c>
-    </row>
-    <row r="32"/>
+        <v>229.232</v>
+      </c>
+    </row>
     <row r="33">
       <c r="A33" s="26" t="inlineStr">
         <is>
@@ -1044,7 +1029,6 @@
         </is>
       </c>
     </row>
-    <row r="34"/>
     <row r="35" ht="18" customHeight="1" s="17">
       <c r="A35" s="37" t="n"/>
       <c r="B35" s="37" t="n"/>
@@ -1057,33 +1041,28 @@
     </row>
     <row r="37" ht="16.5" customHeight="1" s="17"/>
     <row r="38" ht="16.5" customHeight="1" s="17"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
     <row r="42" ht="19.5" customHeight="1" s="17">
       <c r="A42" s="7" t="n"/>
     </row>
-    <row r="43"/>
     <row r="44">
       <c r="A44" s="5" t="n"/>
     </row>
-    <row r="45"/>
     <row r="46">
       <c r="A46" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
     <mergeCell ref="A10:D10"/>
     <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B28:C28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B36:C36"/>
     <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="B31:C31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
